--- a/Documentation/Product Features Scores/Product_Feature_Scores.xlsx
+++ b/Documentation/Product Features Scores/Product_Feature_Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Product Features Scores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6549854-8BE9-423F-9DF6-7FE80D801C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE6D037-2B88-4252-B0B5-BC45BF941115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Scores" sheetId="1" r:id="rId1"/>
@@ -3852,7 +3852,7 @@
         <v>4</v>
       </c>
       <c r="H30" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I30" s="2">
         <v>3</v>
